--- a/05_Figures/F06_prediction/proteins/training/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_1rm_legpress/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -128,34 +128,46 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">SLMAP</t>
+  </si>
+  <si>
     <t xml:space="preserve">TXNDC17</t>
   </si>
   <si>
     <t xml:space="preserve">ACSL3</t>
   </si>
   <si>
+    <t xml:space="preserve">ATP1A2</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRIP2</t>
   </si>
   <si>
     <t xml:space="preserve">CSTB</t>
   </si>
   <si>
+    <t xml:space="preserve">DCXR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPO</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPP2R5D</t>
   </si>
   <si>
-    <t xml:space="preserve">SLMAP</t>
+    <t xml:space="preserve">SGCD</t>
   </si>
   <si>
     <t xml:space="preserve">ANKRD2</t>
   </si>
   <si>
-    <t xml:space="preserve">ATP1A2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ATP5ME</t>
   </si>
   <si>
-    <t xml:space="preserve">DCXR</t>
+    <t xml:space="preserve">CHP1</t>
   </si>
   <si>
     <t xml:space="preserve">ERP44</t>
@@ -170,138 +182,138 @@
     <t xml:space="preserve">IDH1</t>
   </si>
   <si>
-    <t xml:space="preserve">IMPA2</t>
+    <t xml:space="preserve">CDNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECH1</t>
   </si>
   <si>
     <t xml:space="preserve">ISOC2</t>
   </si>
   <si>
-    <t xml:space="preserve">SGCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECH1</t>
+    <t xml:space="preserve">MUSTN1</t>
   </si>
   <si>
     <t xml:space="preserve">PNPO</t>
   </si>
   <si>
+    <t xml:space="preserve">ACYP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUDT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBB2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADSS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IL18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPEPPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXNRD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCDC22</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPL19</t>
   </si>
   <si>
+    <t xml:space="preserve">TXN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQCRFS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD6IP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">SH3BGRL</t>
   </si>
   <si>
-    <t xml:space="preserve">ACYP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IL18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUSTN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPEPPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBB2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXNRD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADSS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DBT</t>
+    <t xml:space="preserve">AP1G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFDN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQCRC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD23B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHCR24</t>
   </si>
   <si>
     <t xml:space="preserve">EIF3F</t>
   </si>
   <si>
-    <t xml:space="preserve">TXN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRFS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP1G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHCR24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFDN5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX7A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX5</t>
-  </si>
-  <si>
     <t xml:space="preserve">IBA57</t>
   </si>
   <si>
@@ -317,6 +329,9 @@
     <t xml:space="preserve">MGST2</t>
   </si>
   <si>
+    <t xml:space="preserve">MRPL22</t>
+  </si>
+  <si>
     <t xml:space="preserve">NSFL1C</t>
   </si>
   <si>
@@ -326,228 +341,225 @@
     <t xml:space="preserve">PRMT5</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMC4</t>
-  </si>
-  <si>
     <t xml:space="preserve">PSMD14</t>
   </si>
   <si>
     <t xml:space="preserve">RAB1A</t>
   </si>
   <si>
-    <t xml:space="preserve">RAD23B</t>
+    <t xml:space="preserve">RPL17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNJ2BP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPD52L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQCRH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIRP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACACB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFG3L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BZW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCUN1D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPYSL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAHD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GART</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GATD3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPHN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPNA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMCD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBNL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLRX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIP4K2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAP1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNH1</t>
   </si>
   <si>
     <t xml:space="preserve">RPL24</t>
   </si>
   <si>
+    <t xml:space="preserve">RPS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRAS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC1A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLIRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMPX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX3</t>
+  </si>
+  <si>
     <t xml:space="preserve">SRSF2</t>
   </si>
   <si>
-    <t xml:space="preserve">SYNJ2BP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPD52L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XIRP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACACB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFG3L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BZW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX7A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCUN1D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPYSL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAHD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GART</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GATD3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GGCT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPHN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KCTD12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPNA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMCD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NLRX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIP4K2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAP1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRAS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SKP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC1A4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLIRP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMPX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX3</t>
-  </si>
-  <si>
     <t xml:space="preserve">SRSF3</t>
   </si>
   <si>
@@ -564,6 +576,9 @@
   </si>
   <si>
     <t xml:space="preserve">VCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZYX</t>
   </si>
 </sst>
 </file>
@@ -950,16 +965,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.619717214335309</v>
+        <v>-0.344448698532861</v>
       </c>
       <c r="I2" t="n">
-        <v>0.112583878722935</v>
+        <v>0.0993387165202365</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -983,29 +998,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.619717214335309</v>
+        <v>-0.344448698532861</v>
       </c>
       <c r="I3" t="n">
-        <v>0.112583878722935</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.507462686567164</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.308457711442786</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.695037320398334</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.757840198018641</v>
-      </c>
+        <v>0.0993387165202365</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1029,2206 +1036,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.718873770484974</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.07866038318414</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.270772282204839</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-2.43056445957073</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.27943412896713</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.2696532957331</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.610809755553351</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.761279710915825</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.90378433704935</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.933221691076333</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.948906873754497</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.337387780604347</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.644602724510643</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.70203535740285</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.694153333248366</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.383515816313503</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.344083658390284</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.581389476837938</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.799632760883183</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.882159511684327</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.800255412371195</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.132632662873139</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.165732767903855</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.32563910189044</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.99881899654331</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.0438998693988346</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.432795897701285</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.0282422452219593</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.858896604264224</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.560128999066297</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.55274948233765</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.19088299262672</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.21530111946513</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.346914086847437</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.126157630389927</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-1.42196897941831</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.347024152303641</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.57227652748041</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.320950160974852</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.372812459645252</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.463884089823337</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.0108035038979933</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-3.03963133756272</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.13515063158866</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.12090809649381</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-1.25334798163488</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.652207823533154</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.498572304318333</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.15669143046135</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-2.52954407174356</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.560488288602789</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.970171833955651</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.28541815176428</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.0154203656682039</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.442046986178605</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.164917959262995</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.0582024667181892</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.195975233870822</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-2.73859458803237</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.363735612969176</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.163766661454183</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-1.06955345821575</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.332251286496119</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.00702167423507</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.333803711027265</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.0287358911591423</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.394980741589307</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.949332409659734</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.34396087969379</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.576640950223932</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.9421413189122</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.37609184397201</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0.260805640317108</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.10687221730685</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.84186821543092</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.25887071619721</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.34518536454949</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.525388634524362</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.492549301114487</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.891640647396324</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.405945843205361</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.632301703385008</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.0329135757038896</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.125085784199264</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-1.81241210145668</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.921026682061368</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.13559506707504</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.968530504160202</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.580882984799095</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-1.55583238311906</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.18838440060993</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.257531528977112</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.79429280150266</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.612034225374358</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.681861612677619</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.0971203578726413</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.0638304400624341</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-1.14175042677205</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-1.27939578966735</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.381385116226506</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.243191559814991</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.566396889885234</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.852833520876545</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-1.61884129940968</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.681451937386852</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-2.51636112474947</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-1.3325163607016</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.720048211312833</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.598501720050375</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.2592410609732</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.664748575483598</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0.122152194793121</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.787142207283668</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0.373415764728267</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.0849712187856451</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.861184625028934</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-2.70980972674985</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-2.19490299893314</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.500946853187527</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0.778032421839029</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.6845687321492</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.064829655705587</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.671202617710822</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-1.36646217110738</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.93605226398559</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-1.18053068060964</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>0.204961555266509</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.464311072895976</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.07746650182297</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0.363745412359753</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-1.16627052192214</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.16240736889682</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.190610930701246</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>0.240877741588798</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-1.5106795154639</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.515593843818244</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0.70435629559041</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0.115282338665705</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0.26873827324536</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.177205685206478</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.349886320845113</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0.126314995887077</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.744677530441718</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.303670253341771</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>0.160145265003957</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.355858431520326</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.210400796363535</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-1.02592874124948</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-1.95415758999684</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-2.53440387222331</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.6388718570307</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-1.40176054941299</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.347163946096433</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.0310137517001428</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.9747143605583</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-1.36081761005099</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.207167181112077</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.350438464524549</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.638372569508289</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-1.00436316544915</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.00829508142770097</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.85768830565942</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-1.75242889741264</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.733585281593349</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.809840568308302</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>0.41134383436013</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-1.72767043997769</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.170369306301673</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-1.09709539561106</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.142762609066033</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.258866736872442</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.309136590756404</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.994608462674084</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.635513848976291</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.44554760591739</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.848511409853996</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.0380287281198188</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>0.502739455480612</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.217516104026696</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.451071064211736</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.726290849574932</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.392111621397639</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-3.03087354552888</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-1.46312123348602</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.431892071664408</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-1.71732733013406</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.754778713523651</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.486840565373339</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-1.22844129741938</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.165345553963988</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-2.95713102954907</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.444452240596772</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.948934596809488</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-2.35942997578512</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>0.0446453955028524</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.594054082694942</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.926723071638965</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>0.645091097743523</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.794662035148433</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-1.9323271386343</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3271,7 +1078,7 @@
         <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>52.363541589614</v>
+        <v>50.2403396721805</v>
       </c>
     </row>
     <row r="3">
@@ -3288,7 +1095,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>54.432748472688</v>
+        <v>56.2026962281106</v>
       </c>
     </row>
     <row r="4">
@@ -3305,7 +1112,7 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>39.5457632597217</v>
+        <v>42.7056262981924</v>
       </c>
     </row>
     <row r="5">
@@ -3322,7 +1129,7 @@
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>57.4726308484367</v>
+        <v>56.4013212521952</v>
       </c>
     </row>
     <row r="6">
@@ -3339,7 +1146,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>36.8337003005459</v>
+        <v>37.99661081272</v>
       </c>
     </row>
     <row r="7">
@@ -3356,7 +1163,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>30.7449257103525</v>
+        <v>28.2181262257578</v>
       </c>
     </row>
     <row r="8">
@@ -3373,7 +1180,7 @@
         <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>39.4848019083379</v>
+        <v>41.9612398862991</v>
       </c>
     </row>
     <row r="9">
@@ -3390,7 +1197,7 @@
         <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>44.5821095879105</v>
+        <v>43.3260153797549</v>
       </c>
     </row>
     <row r="10">
@@ -3407,7 +1214,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>102.390858542283</v>
+        <v>84.4098093662816</v>
       </c>
     </row>
     <row r="11">
@@ -3424,7 +1231,7 @@
         <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>37.3737954112027</v>
+        <v>36.1393108852677</v>
       </c>
     </row>
     <row r="12">
@@ -3441,7 +1248,7 @@
         <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.62602972380485</v>
+        <v>-0.127989833539651</v>
       </c>
     </row>
     <row r="13">
@@ -3458,7 +1265,7 @@
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>23.8103593194361</v>
+        <v>23.1715989220211</v>
       </c>
     </row>
     <row r="14">
@@ -3475,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>69.000226151946</v>
+        <v>68.794020367571</v>
       </c>
     </row>
     <row r="15">
@@ -3492,7 +1299,7 @@
         <v>89</v>
       </c>
       <c r="E15" t="n">
-        <v>51.8276038931918</v>
+        <v>52.4395397150773</v>
       </c>
     </row>
   </sheetData>
@@ -3551,10 +1358,10 @@
         <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928571428571429</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3636,10 +1443,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="9">
@@ -3653,10 +1460,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="10">
@@ -3670,10 +1477,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="11">
@@ -3687,10 +1494,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="12">
@@ -3704,10 +1511,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.857142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="13">
@@ -3823,10 +1630,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.785714285714286</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="20">
@@ -4010,10 +1817,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="31">
@@ -4027,10 +1834,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="32">
@@ -4044,10 +1851,10 @@
         <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="33">
@@ -4112,10 +1919,10 @@
         <v>71</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="37">
@@ -4129,10 +1936,10 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="38">
@@ -4146,10 +1953,10 @@
         <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -4163,10 +1970,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
@@ -4214,10 +2021,10 @@
         <v>77</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="43">
@@ -4231,10 +2038,10 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="44">
@@ -4248,10 +2055,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="45">
@@ -4265,10 +2072,10 @@
         <v>80</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="46">
@@ -4333,10 +2140,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>0.285714285714286</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="50">
@@ -4367,10 +2174,10 @@
         <v>86</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="52">
@@ -4384,10 +2191,10 @@
         <v>87</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="53">
@@ -4401,10 +2208,10 @@
         <v>88</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="54">
@@ -4418,10 +2225,10 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="55">
@@ -4469,10 +2276,10 @@
         <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="58">
@@ -4486,10 +2293,10 @@
         <v>93</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>0.142857142857143</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="59">
@@ -4843,10 +2650,10 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="80">
@@ -4860,10 +2667,10 @@
         <v>115</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="81">
@@ -6002,6 +3809,91 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="s">
+        <v>183</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="s">
+        <v>184</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="s">
+        <v>185</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="s">
+        <v>186</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="s">
+        <v>187</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/training/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_1rm_legpress/spls/c_data/results.xlsx
@@ -1001,7 +1001,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.344448698532861</v>
@@ -1009,10 +1009,18 @@
       <c r="I3" t="n">
         <v>0.0993387165202365</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.36318407960199</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.303482587064677</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.688498524362378</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.740423337833227</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1036,6 +1044,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.757151596415969</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.25193632827886</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.240145304503259</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-2.35093519919996</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.2633277463744</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.951327023442504</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.590559001268736</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.79171634765898</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.98578496608818</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.882735903724223</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.87002115942202</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.435487710861558</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.759647355663747</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.01455645792585</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.699469975965191</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.19753891016456</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.356840080077406</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.556443927672731</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.446472994412639</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.790169823139278</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.79146768689607</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.16349481897655</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.260967679294578</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.26656823860441</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.00293149697738</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0398092367904076</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.47146687631847</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.136830579607903</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.93268441740955</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.493573391915548</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.57333292642535</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.13828732546495</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.35857674033279</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.421011798625608</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.251729180098073</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1.34645682838619</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.479151955622703</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.810975243037</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.256004679750947</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.400050015205921</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.767191384372212</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.250091356419271</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.87491002172996</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0654177920617075</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.0352881316345</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.22568437372645</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.825815627238467</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.436777947950523</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.0873327938240209</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-2.64691299359576</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.563461341694594</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.781699533684995</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.161324710750026</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.169865976693258</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.370915679297968</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.262872084007547</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.028629331086106</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.0514140694776549</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-2.65462600982841</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.313210080310627</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.100826525207524</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-2.25591460665666</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.35522286182789</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.10980133458123</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.222933906465685</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.0632402445955531</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.333764601184815</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.02648943257157</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.06716408303635</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.54093243860186</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.964077032648903</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.12027949019063</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.283755234569718</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.334763521840258</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-2.05098256916615</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.51704662173826</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.372407669428946</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.51564015251438</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.243532813712465</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.866848942054826</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.359854665439232</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.627334070792706</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.0244863589191137</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.212587235651552</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-1.89906496997654</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.708042474356136</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.14165520988645</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.893352069298107</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.586316241003857</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.38806001621814</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.17535728869022</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.25626518072988</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.38983303669251</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.826795890547912</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.648652483419697</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.168539014177037</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.0414362389251499</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.418555787679079</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.30483503626237</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.334141092666832</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.425520834344566</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.833221928733144</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.978733917968315</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-1.4531790455214</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.724021514426904</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-2.31768524324602</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.12909820978181</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.714353685663475</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.644790778745716</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.262868447061918</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.637545606944661</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.134704880414896</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.814491533193458</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.376161317914498</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.291770232443805</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.883220136622348</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-2.57650338467228</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-2.17821719120215</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.52912629669569</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.782472914368269</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.728228952111891</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.0285011689108976</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.731988942620543</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-1.34976523027535</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-2.12087551165209</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.3728676400109</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.187584218225518</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.434953178680246</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.984307441279625</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.411880596517889</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.883184844767166</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.00203757503196855</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.191269773308062</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.223224648171504</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-1.48405712402746</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.44949963796793</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.716846165752727</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.0580518446620251</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.255756106224115</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.128432503818133</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.302958962786507</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.0610556955198731</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.575454925951558</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.422426551841434</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.0967753197924528</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.273594775400635</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.182571477097651</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.752417235470849</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.93617111525127</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-1.89087830698701</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.566178433709668</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1.50854320404586</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.25493392251697</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.0144613169689551</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.641534343988433</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.1886098251553</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.00424411655979773</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.312811167579006</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.629596490768134</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.851248669626208</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.0178799009177225</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.971750319733969</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-1.94713612371383</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.791579206736191</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.760657850078175</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.476854953257346</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1.46540913825665</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.189158143772165</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.01975204915162</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.269603609684032</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.120389469197799</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.354410483429704</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.714836067410172</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.0389264411357231</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.25161991246499</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1.00710476943912</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.130497361862782</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.412526562411782</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.209037975453818</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.789543320862236</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.723739374961396</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.437466859769736</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-3.43473595856815</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1.43969664974322</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.19743200253032</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.57431321915043</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.63454954030986</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.361492379627994</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1.39910753619044</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.0949403386083871</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-2.54085337954146</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.741885231276606</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.984745688647484</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-2.37807106017041</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.0261192553639319</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.477296020338851</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.74630055794112</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.644808311643418</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.807626151743387</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.88662645331533</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
